--- a/api_test_report.xlsx
+++ b/api_test_report.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -534,21 +534,21 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/auth/register</t>
+          <t>/stats</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Register user</t>
+          <t>Service statistics</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -568,16 +568,16 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/auth/login</t>
+          <t>/api/v1/auth/register</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Login user</t>
+          <t>Register user</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -592,17 +592,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/auth/me</t>
+          <t>/api/v1/auth/login</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Get current user</t>
+          <t>Login user</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -631,11 +631,11 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Invalid token</t>
+          <t>Get current user</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>401</v>
+        <v>200</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -650,21 +650,21 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/posts</t>
+          <t>/api/v1/auth/me</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Create post</t>
+          <t>Invalid token</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -689,11 +689,11 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>List posts</t>
+          <t>Create post</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/posts/{post_id}</t>
+          <t>/api/v1/posts</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Get post</t>
+          <t>List posts</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -737,7 +737,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Update post</t>
+          <t>Get post</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -766,28 +766,57 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/posts/{post_id}</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Update post</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>/api/v1/posts/{post_id}</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Delete post</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E12" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
